--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Netherlands Eredivisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Netherlands Eredivisie_20242025.xlsx
@@ -67643,13 +67643,13 @@
         <v>4</v>
       </c>
       <c r="AX308" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY308" t="n">
         <v>12</v>
       </c>
       <c r="AZ308" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA308" t="n">
         <v>4</v>
@@ -67852,19 +67852,19 @@
         <v>2.87</v>
       </c>
       <c r="AU309" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV309" t="n">
         <v>8</v>
       </c>
       <c r="AW309" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX309" t="n">
         <v>15</v>
       </c>
       <c r="AY309" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ309" t="n">
         <v>23</v>
@@ -68070,19 +68070,19 @@
         <v>3.13</v>
       </c>
       <c r="AU310" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV310" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW310" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX310" t="n">
         <v>6</v>
       </c>
-      <c r="AV310" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW310" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX310" t="n">
-        <v>7</v>
-      </c>
       <c r="AY310" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ310" t="n">
         <v>11</v>
